--- a/artfynd/A 35274-2021 artfynd.xlsx
+++ b/artfynd/A 35274-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35274-2021 artfynd.xlsx
+++ b/artfynd/A 35274-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1512,6 +1512,121 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130285191</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58198</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flättna grindstuga, östra skogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>618540</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6508538</v>
+      </c>
+      <c r="S9" t="n">
+        <v>150</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mikael Ackelman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Ackelman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35274-2021 artfynd.xlsx
+++ b/artfynd/A 35274-2021 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>130285191</v>
       </c>
       <c r="B9" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35274-2021 artfynd.xlsx
+++ b/artfynd/A 35274-2021 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>130285191</v>
       </c>
       <c r="B9" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35274-2021 artfynd.xlsx
+++ b/artfynd/A 35274-2021 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>130285191</v>
       </c>
       <c r="B9" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35274-2021 artfynd.xlsx
+++ b/artfynd/A 35274-2021 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>130285191</v>
       </c>
       <c r="B9" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35274-2021 artfynd.xlsx
+++ b/artfynd/A 35274-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53899147</v>
+        <v>53885119</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grindstugan 375 m o, Srm</t>
+          <t>lilla Flättna 5 700 m vnv, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618522.3325657614</v>
+        <v>618620</v>
       </c>
       <c r="R2" t="n">
-        <v>6508421.291419217</v>
+        <v>6508675</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,27 +745,18 @@
           <t>2015-06-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-06-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,53 +775,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53899408</v>
+        <v>53899407</v>
       </c>
       <c r="B3" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grindstugan 375 m ono, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618503.9957487779</v>
+        <v>618504</v>
       </c>
       <c r="R3" t="n">
-        <v>6508595.43984567</v>
+        <v>6508595</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,27 +845,18 @@
           <t>2015-06-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-06-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,56 +875,63 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53899293</v>
+        <v>53899411</v>
       </c>
       <c r="B4" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grindstugan 375 m o, Srm</t>
+          <t>Grindstugan 375 m ono, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618522.3325657614</v>
+        <v>618504</v>
       </c>
       <c r="R4" t="n">
-        <v>6508421.291419217</v>
+        <v>6508595</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,19 +958,9 @@
           <t>2015-06-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-06-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,19 +987,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>53899411</v>
+        <v>90557223</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1062,30 +1020,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grindstugan 375 m ono, Srm</t>
+          <t>Flättna grindstuga, östra skogen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618503.9957487779</v>
+        <v>618540</v>
       </c>
       <c r="R5" t="n">
-        <v>6508595.43984567</v>
+        <v>6508538</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1064,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,67 +1094,71 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Lars Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Lars Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53899407</v>
+        <v>53899266</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>102992</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Näktergal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Luscinia luscinia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grindstugan 375 m ono, Srm</t>
+          <t>Grindstugan 375 m o, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618503.9957487779</v>
+        <v>618522</v>
       </c>
       <c r="R6" t="n">
-        <v>6508595.43984567</v>
+        <v>6508421</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,28 +1185,17 @@
           <t>2015-06-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-06-10</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1266,62 +1214,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>85536035</v>
+        <v>104791291</v>
       </c>
       <c r="B7" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flättna grindstuga, östra skogen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618540.1347001961</v>
+        <v>618540</v>
       </c>
       <c r="R7" t="n">
-        <v>6508537.787629374</v>
+        <v>6508538</v>
       </c>
       <c r="S7" t="n">
         <v>150</v>
@@ -1348,22 +1288,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2022-11-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2022-11-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,49 +1318,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Karlsson</t>
+          <t>Björn Erixon</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Karlsson, Jan Gustafsson</t>
+          <t>Björn Erixon</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>90557223</v>
+        <v>85536035</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1432,7 +1367,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1442,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618540.1347001961</v>
+        <v>618540</v>
       </c>
       <c r="R8" t="n">
-        <v>6508537.787629374</v>
+        <v>6508538</v>
       </c>
       <c r="S8" t="n">
         <v>150</v>
@@ -1472,22 +1407,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2021-01-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,22 +1437,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Danielsson</t>
+          <t>Jan Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Danielsson</t>
+          <t>Jan Karlsson, Jan Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130285191</v>
+        <v>53899147</v>
       </c>
       <c r="B9" t="n">
-        <v>58235</v>
+        <v>106156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,45 +1460,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flättna grindstuga, östra skogen, Srm</t>
+          <t>Grindstugan 375 m o, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618540</v>
+        <v>618522</v>
       </c>
       <c r="R9" t="n">
-        <v>6508538</v>
+        <v>6508421</v>
       </c>
       <c r="S9" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,22 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2015-06-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2015-06-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,15 +1541,215 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mikael Ackelman</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mikael Ackelman</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>53899293</v>
+      </c>
+      <c r="B10" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grindstugan 375 m o, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>618522</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6508421</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-06-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-06-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>53899408</v>
+      </c>
+      <c r="B11" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grindstugan 375 m ono, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>618504</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6508595</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-06-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-06-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
